--- a/artfynd/A 32199-2023 artfynd.xlsx
+++ b/artfynd/A 32199-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32199-2023 artfynd.xlsx
+++ b/artfynd/A 32199-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104622551</v>
+        <v>104681075</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591264.8652523692</v>
+        <v>591279</v>
       </c>
       <c r="R2" t="n">
-        <v>7043217.144234532</v>
+        <v>7043191</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -746,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>08:45</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>08:45</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,69 +757,67 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104622518</v>
+        <v>104681101</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>48</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591225.9893459696</v>
+        <v>591321</v>
       </c>
       <c r="R3" t="n">
-        <v>7043215.583779484</v>
+        <v>7043160</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -859,22 +844,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>08:45</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>08:45</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,69 +858,65 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104622823</v>
+        <v>111267164</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591305.7109081034</v>
+        <v>591635</v>
       </c>
       <c r="R4" t="n">
-        <v>7043165.596235943</v>
+        <v>7043404</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,22 +943,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>08:45</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>08:45</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,27 +963,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Råghall, Lina Hällström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104681051</v>
+        <v>111273664</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,45 +986,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>48</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591251.4437989765</v>
+        <v>591673</v>
       </c>
       <c r="R5" t="n">
-        <v>7043185.932821126</v>
+        <v>7043420</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,22 +1040,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,34 +1054,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104681045</v>
+        <v>111315151</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,42 +1083,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>48</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591249.3105024131</v>
+        <v>591671</v>
       </c>
       <c r="R6" t="n">
-        <v>7043197.93442897</v>
+        <v>7043423</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1213,22 +1137,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,34 +1151,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Johan Råghall, Lina Hällström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104681082</v>
+        <v>104622760</v>
       </c>
       <c r="B7" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,42 +1180,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Getstugeberget, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591298.2133711505</v>
+        <v>591329</v>
       </c>
       <c r="R7" t="n">
-        <v>7043177.444135577</v>
+        <v>7043171</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1334,22 +1235,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,27 +1265,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104681048</v>
+        <v>104680980</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1419,10 +1315,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591249.3105024131</v>
+        <v>591184</v>
       </c>
       <c r="R8" t="n">
-        <v>7043197.93442897</v>
+        <v>7043182</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1452,19 +1348,9 @@
           <t>2022-11-15</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-11-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,37 +1378,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104681075</v>
+        <v>104680988</v>
       </c>
       <c r="B9" t="n">
-        <v>89577</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1535,10 +1416,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591279.0299158915</v>
+        <v>591204</v>
       </c>
       <c r="R9" t="n">
-        <v>7043191.190934213</v>
+        <v>7043191</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1568,19 +1449,9 @@
           <t>2022-11-15</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-11-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,15 +1479,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104681053</v>
+        <v>104681080</v>
       </c>
       <c r="B10" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1624,21 +1490,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1651,10 +1517,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591251.4437989765</v>
+        <v>591298</v>
       </c>
       <c r="R10" t="n">
-        <v>7043185.932821126</v>
+        <v>7043177</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1684,19 +1550,9 @@
           <t>2022-11-15</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-11-15</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1724,15 +1580,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104681080</v>
+        <v>104681092</v>
       </c>
       <c r="B11" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,12 +1600,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1767,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591298.2133711505</v>
+        <v>591312</v>
       </c>
       <c r="R11" t="n">
-        <v>7043177.444135577</v>
+        <v>7043163</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1800,19 +1651,9 @@
           <t>2022-11-15</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-11-15</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,47 +1681,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104681033</v>
+        <v>104681097</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1888,10 +1719,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591211.9666893056</v>
+        <v>591327</v>
       </c>
       <c r="R12" t="n">
-        <v>7043205.353362232</v>
+        <v>7043174</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1921,19 +1752,9 @@
           <t>2022-11-15</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-11-15</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1961,15 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104681041</v>
+        <v>104681103</v>
       </c>
       <c r="B13" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,21 +1793,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2004,10 +1820,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>591211.9666893056</v>
+        <v>591321</v>
       </c>
       <c r="R13" t="n">
-        <v>7043205.353362232</v>
+        <v>7043160</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2037,19 +1853,9 @@
           <t>2022-11-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-11-15</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2077,15 +1883,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104622738</v>
+        <v>107173482</v>
       </c>
       <c r="B14" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,35 +1894,35 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>591370.1294540192</v>
+        <v>591195</v>
       </c>
       <c r="R14" t="n">
-        <v>7043181.293393185</v>
+        <v>7043190</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2148,22 +1949,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
+          <t>2023-03-07</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
+          <t>2023-03-07</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2178,27 +1979,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104622636</v>
+        <v>111268460</v>
       </c>
       <c r="B15" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,35 +2002,35 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>591343.9067822314</v>
+        <v>591473</v>
       </c>
       <c r="R15" t="n">
-        <v>7043222.090614219</v>
+        <v>7043318</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2261,22 +2057,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>08:45</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>08:45</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,27 +2077,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Råghall, Lina Hällström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104622742</v>
+        <v>111273661</v>
       </c>
       <c r="B16" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2319,38 +2100,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>591361.4199005438</v>
+        <v>591637</v>
       </c>
       <c r="R16" t="n">
-        <v>7043173.001690743</v>
+        <v>7043423</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2374,22 +2154,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>08:45</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>08:45</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2404,27 +2174,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104622760</v>
+        <v>111273663</v>
       </c>
       <c r="B17" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2441,29 +2206,28 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>591328.3800968044</v>
+        <v>591652</v>
       </c>
       <c r="R17" t="n">
-        <v>7043170.713859768</v>
+        <v>7043414</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2487,22 +2251,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>08:45</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>08:45</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2517,27 +2271,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104622646</v>
+        <v>111315143</v>
       </c>
       <c r="B18" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2545,35 +2294,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>591380.186519376</v>
+        <v>591478</v>
       </c>
       <c r="R18" t="n">
-        <v>7043267.360629026</v>
+        <v>7043320</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2600,22 +2348,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>08:45</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>08:45</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2630,27 +2368,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Råghall, Lina Hällström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104681092</v>
+        <v>111315148</v>
       </c>
       <c r="B19" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2667,28 +2400,25 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>591311.6115370012</v>
+        <v>591645</v>
       </c>
       <c r="R19" t="n">
-        <v>7043162.637983168</v>
+        <v>7043408</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2715,22 +2445,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2739,34 +2459,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Johan Råghall, Lina Hällström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104681102</v>
+        <v>111315149</v>
       </c>
       <c r="B20" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2774,38 +2488,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>591320.6412087205</v>
+        <v>591671</v>
       </c>
       <c r="R20" t="n">
-        <v>7043159.769446937</v>
+        <v>7043423</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2832,22 +2542,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2862,70 +2562,58 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Johan Råghall, Lina Hällström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>104681090</v>
+        <v>104622518</v>
       </c>
       <c r="B21" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Getstugeberget, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>591311.6115370012</v>
+        <v>591226</v>
       </c>
       <c r="R21" t="n">
-        <v>7043162.637983168</v>
+        <v>7043215</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2952,22 +2640,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2976,77 +2664,64 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104681096</v>
+        <v>104622636</v>
       </c>
       <c r="B22" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Getstugeberget, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>591327.3964939628</v>
+        <v>591343</v>
       </c>
       <c r="R22" t="n">
-        <v>7043173.813054159</v>
+        <v>7043222</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3073,22 +2748,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3097,34 +2772,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>104681103</v>
+        <v>104622823</v>
       </c>
       <c r="B23" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3132,37 +2801,35 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Getstugeberget, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>591320.6412087205</v>
+        <v>591306</v>
       </c>
       <c r="R23" t="n">
-        <v>7043159.769446937</v>
+        <v>7043166</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3189,22 +2856,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3213,56 +2880,50 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>104681101</v>
+        <v>104681041</v>
       </c>
       <c r="B24" t="n">
-        <v>89577</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>48</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3275,10 +2936,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>591320.6412087205</v>
+        <v>591212</v>
       </c>
       <c r="R24" t="n">
-        <v>7043159.769446937</v>
+        <v>7043205</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3308,19 +2969,9 @@
           <t>2022-11-15</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-11-15</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3348,15 +2999,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>104681097</v>
+        <v>104681048</v>
       </c>
       <c r="B25" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3364,21 +3010,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3391,10 +3037,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>591327.3964939628</v>
+        <v>591249</v>
       </c>
       <c r="R25" t="n">
-        <v>7043173.813054159</v>
+        <v>7043198</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3424,19 +3070,9 @@
           <t>2022-11-15</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-11-15</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3464,15 +3100,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111273661</v>
+        <v>104681053</v>
       </c>
       <c r="B26" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3480,37 +3111,40 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>591636.9769660851</v>
+        <v>591251</v>
       </c>
       <c r="R26" t="n">
-        <v>7043422.612332962</v>
+        <v>7043186</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3534,22 +3168,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3558,33 +3182,29 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111273656</v>
+        <v>111315142</v>
       </c>
       <c r="B27" t="n">
-        <v>73696</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3592,21 +3212,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3616,13 +3236,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>591725.0424782543</v>
+        <v>591469</v>
       </c>
       <c r="R27" t="n">
-        <v>7043424.7006835</v>
+        <v>7043315</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3649,19 +3269,9 @@
           <t>2023-08-04</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3676,27 +3286,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Johan Råghall, Lina Hällström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>111273663</v>
+        <v>111273659</v>
       </c>
       <c r="B28" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3704,21 +3309,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3728,10 +3333,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>591652.4436271309</v>
+        <v>591495</v>
       </c>
       <c r="R28" t="n">
-        <v>7043413.675855185</v>
+        <v>7043328</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3761,19 +3366,9 @@
           <t>2023-08-04</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3800,15 +3395,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>111273670</v>
+        <v>111273660</v>
       </c>
       <c r="B29" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3816,21 +3406,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3840,10 +3430,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>591622.4606337334</v>
+        <v>591641</v>
       </c>
       <c r="R29" t="n">
-        <v>7043398.517451782</v>
+        <v>7043417</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3873,19 +3463,9 @@
           <t>2023-08-04</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3912,19 +3492,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>111273659</v>
+        <v>111315145</v>
       </c>
       <c r="B30" t="n">
-        <v>89845</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3937,12 +3512,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3952,13 +3527,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>591495.2093399345</v>
+        <v>591479</v>
       </c>
       <c r="R30" t="n">
-        <v>7043327.847347787</v>
+        <v>7043315</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3985,19 +3560,9 @@
           <t>2023-08-04</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4012,65 +3577,61 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Johan Råghall, Lina Hällström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111273666</v>
+        <v>107173505</v>
       </c>
       <c r="B31" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>591499.5271172373</v>
+        <v>591183</v>
       </c>
       <c r="R31" t="n">
-        <v>7043317.696102448</v>
+        <v>7043190</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4094,22 +3655,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2023-03-07</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2023-03-07</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4124,49 +3685,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>111273655</v>
+        <v>111315150</v>
       </c>
       <c r="B32" t="n">
-        <v>73696</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4176,13 +3732,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>591622.4606337334</v>
+        <v>591671</v>
       </c>
       <c r="R32" t="n">
-        <v>7043398.517451782</v>
+        <v>7043415</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4209,19 +3765,9 @@
           <t>2023-08-04</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4236,31 +3782,26 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Johan Råghall, Lina Hällström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>111273672</v>
+        <v>111266309</v>
       </c>
       <c r="B33" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4282,19 +3823,20 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>591719.3732997013</v>
+        <v>591747</v>
       </c>
       <c r="R33" t="n">
-        <v>7043419.6232786</v>
+        <v>7043436</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4321,19 +3863,9 @@
           <t>2023-08-04</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4348,27 +3880,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Johan Råghall, Lina Hällström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>111273660</v>
+        <v>111273669</v>
       </c>
       <c r="B34" t="n">
-        <v>89845</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4376,21 +3903,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4400,10 +3927,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>591641.1794901572</v>
+        <v>591617</v>
       </c>
       <c r="R34" t="n">
-        <v>7043416.478903031</v>
+        <v>7043378</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4433,19 +3960,9 @@
           <t>2023-08-04</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4472,19 +3989,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>111273669</v>
+        <v>111273670</v>
       </c>
       <c r="B35" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4512,10 +4024,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>591616.806528918</v>
+        <v>591623</v>
       </c>
       <c r="R35" t="n">
-        <v>7043377.357856153</v>
+        <v>7043398</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4545,19 +4057,9 @@
           <t>2023-08-04</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4584,37 +4086,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>111273667</v>
+        <v>111273672</v>
       </c>
       <c r="B36" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4624,10 +4121,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>591618.866522243</v>
+        <v>591719</v>
       </c>
       <c r="R36" t="n">
-        <v>7043352.399297187</v>
+        <v>7043420</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4657,19 +4154,9 @@
           <t>2023-08-04</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4696,15 +4183,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>111273664</v>
+        <v>111315138</v>
       </c>
       <c r="B37" t="n">
-        <v>89590</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4712,21 +4194,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>48</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4736,13 +4218,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>591673.2841504611</v>
+        <v>591721</v>
       </c>
       <c r="R37" t="n">
-        <v>7043420.083276978</v>
+        <v>7043369</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4769,19 +4251,9 @@
           <t>2023-08-04</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4796,27 +4268,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Johan Råghall, Lina Hällström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>111315145</v>
+        <v>111315146</v>
       </c>
       <c r="B38" t="n">
-        <v>89845</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4824,21 +4291,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4848,10 +4315,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>591478.5830416525</v>
+        <v>591617</v>
       </c>
       <c r="R38" t="n">
-        <v>7043314.860723522</v>
+        <v>7043365</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4881,19 +4348,9 @@
           <t>2023-08-04</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4920,15 +4377,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>111315149</v>
+        <v>111266420</v>
       </c>
       <c r="B39" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4936,34 +4388,35 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>591670.9593730925</v>
+        <v>591723</v>
       </c>
       <c r="R39" t="n">
-        <v>7043423.143536596</v>
+        <v>7043410</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4993,19 +4446,9 @@
           <t>2023-08-04</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5032,15 +4475,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>111315148</v>
+        <v>111273655</v>
       </c>
       <c r="B40" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5048,21 +4486,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5072,13 +4510,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>591645.4590963478</v>
+        <v>591623</v>
       </c>
       <c r="R40" t="n">
-        <v>7043407.667238996</v>
+        <v>7043398</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5105,19 +4543,9 @@
           <t>2023-08-04</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5132,27 +4560,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Johan Råghall, Lina Hällström</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>111268460</v>
+        <v>111273656</v>
       </c>
       <c r="B41" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5160,38 +4583,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>591472.6953434804</v>
+        <v>591725</v>
       </c>
       <c r="R41" t="n">
-        <v>7043317.372138057</v>
+        <v>7043425</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5218,19 +4640,9 @@
           <t>2023-08-04</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5245,27 +4657,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Johan Råghall, Lina Hällström</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>111266420</v>
+        <v>111315147</v>
       </c>
       <c r="B42" t="n">
-        <v>73696</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5291,17 +4698,16 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>591722.3379231346</v>
+        <v>591620</v>
       </c>
       <c r="R42" t="n">
-        <v>7043409.880360964</v>
+        <v>7043403</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5331,19 +4737,9 @@
           <t>2023-08-04</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5370,15 +4766,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>111315146</v>
+        <v>104622646</v>
       </c>
       <c r="B43" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5386,34 +4777,35 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Getstugeberget, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>591616.7319226691</v>
+        <v>591380</v>
       </c>
       <c r="R43" t="n">
-        <v>7043364.400079632</v>
+        <v>7043267</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5440,22 +4832,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5470,63 +4862,58 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Johan Råghall, Lina Hällström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>111267164</v>
+        <v>104622738</v>
       </c>
       <c r="B44" t="n">
-        <v>89590</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>48</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Getstugeberget, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>591635.2558426465</v>
+        <v>591371</v>
       </c>
       <c r="R44" t="n">
-        <v>7043404.693209249</v>
+        <v>7043182</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5553,22 +4940,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5583,27 +4970,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Johan Råghall, Lina Hällström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>111268512</v>
+        <v>104622742</v>
       </c>
       <c r="B45" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5611,40 +4993,35 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Getstugeberget, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>591472.6953434804</v>
+        <v>591361</v>
       </c>
       <c r="R45" t="n">
-        <v>7043317.372138057</v>
+        <v>7043173</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5671,22 +5048,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5701,27 +5078,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Johan Råghall, Lina Hällström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>111315143</v>
+        <v>107173567</v>
       </c>
       <c r="B46" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5729,34 +5101,40 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>591477.5224061215</v>
+        <v>591206</v>
       </c>
       <c r="R46" t="n">
-        <v>7043320.638036993</v>
+        <v>7043182</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5783,22 +5161,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2023-03-07</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2023-03-07</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5813,54 +5191,51 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Johan Råghall, Lina Hällström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>111315139</v>
+        <v>111268512</v>
       </c>
       <c r="B47" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5869,10 +5244,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>591510.9235177813</v>
+        <v>591473</v>
       </c>
       <c r="R47" t="n">
-        <v>7043279.155835367</v>
+        <v>7043318</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5902,24 +5277,9 @@
           <t>2023-08-04</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Plus massor av bladrosetter</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5946,57 +5306,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>111315141</v>
+        <v>111273658</v>
       </c>
       <c r="B48" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>591486.5005135566</v>
+        <v>591851</v>
       </c>
       <c r="R48" t="n">
-        <v>7043319.555657836</v>
+        <v>7043465</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6023,19 +5374,14 @@
           <t>2023-08-04</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2023-08-04</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6050,62 +5396,61 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Johan Råghall, Lina Hällström</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>111315151</v>
+        <v>104681102</v>
       </c>
       <c r="B49" t="n">
-        <v>89590</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>48</v>
+        <v>102612</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>591670.9593730925</v>
+        <v>591321</v>
       </c>
       <c r="R49" t="n">
-        <v>7043423.143536596</v>
+        <v>7043160</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6132,22 +5477,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6162,27 +5497,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Johan Råghall, Lina Hällström</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>111315147</v>
+        <v>104681082</v>
       </c>
       <c r="B50" t="n">
-        <v>73696</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6190,34 +5520,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>591620.5314988887</v>
+        <v>591298</v>
       </c>
       <c r="R50" t="n">
-        <v>7043403.376114395</v>
+        <v>7043177</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6244,22 +5582,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6274,63 +5602,65 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Johan Råghall, Lina Hällström</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>111266309</v>
+        <v>104680978</v>
       </c>
       <c r="B51" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>591747.0822552936</v>
+        <v>591184</v>
       </c>
       <c r="R51" t="n">
-        <v>7043436.057239689</v>
+        <v>7043182</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6357,22 +5687,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6381,68 +5701,72 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Johan Råghall, Lina Hällström</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>111315150</v>
+        <v>104680984</v>
       </c>
       <c r="B52" t="n">
-        <v>89369</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>591671.190636521</v>
+        <v>591194</v>
       </c>
       <c r="R52" t="n">
-        <v>7043415.108879722</v>
+        <v>7043193</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6469,22 +5793,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6493,68 +5807,68 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Johan Råghall, Lina Hällström</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>111315142</v>
+        <v>104680987</v>
       </c>
       <c r="B53" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>591469.6177441666</v>
+        <v>591204</v>
       </c>
       <c r="R53" t="n">
-        <v>7043315.49674286</v>
+        <v>7043191</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6581,22 +5895,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6605,21 +5909,856 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>104681033</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Getstugeberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>591212</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7043205</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>104681045</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Getstugeberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>591249</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7043198</v>
+      </c>
+      <c r="S55" t="n">
+        <v>25</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>104681051</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Getstugeberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>591251</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7043186</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>104681090</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Getstugeberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>591312</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7043163</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>104681096</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Getstugeberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>591327</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7043174</v>
+      </c>
+      <c r="S58" t="n">
+        <v>25</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>111273666</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Getstugeberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>591499</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7043318</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2023-08-04</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2023-08-04</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>111315139</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Getstugeberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>591511</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7043279</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2023-08-04</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2023-08-04</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Plus massor av bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
           <t>Johan Råghall</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
+      <c r="AX60" t="inlineStr">
         <is>
           <t>Johan Råghall, Lina Hällström</t>
         </is>
       </c>
-      <c r="AY53" t="inlineStr"/>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>111315141</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Getstugeberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>591487</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7043320</v>
+      </c>
+      <c r="S61" t="n">
+        <v>25</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2023-08-04</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2023-08-04</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32199-2023 artfynd.xlsx
+++ b/artfynd/A 32199-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AZ61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104681075</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104681101</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111267164</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111273664</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111315151</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104622760</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1375,6 +1410,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104680980</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1476,6 +1516,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104680988</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1577,6 +1622,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104681080</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1678,6 +1728,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104681092</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1779,6 +1834,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104681097</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1880,6 +1940,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104681103</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1988,6 +2053,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107173482</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111268460</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2183,6 +2258,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111273661</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2280,6 +2360,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111273663</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2377,6 +2462,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111315143</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2474,6 +2564,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111315148</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2571,6 +2666,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111315149</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2679,6 +2779,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104622518</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2787,6 +2892,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104622636</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2895,6 +3005,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104622823</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2996,6 +3111,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104681041</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3097,6 +3217,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104681048</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3198,6 +3323,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104681053</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3295,6 +3425,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111315142</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3392,6 +3527,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111273659</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3489,6 +3629,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111273660</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3586,6 +3731,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111315145</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3694,6 +3844,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107173505</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3791,6 +3946,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111315150</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3889,6 +4049,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111266309</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3986,6 +4151,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111273669</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4083,6 +4253,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111273670</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4180,6 +4355,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111273672</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4277,6 +4457,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111315138</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4374,6 +4559,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111315146</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4472,6 +4662,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111266420</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4569,6 +4764,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111273655</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4666,6 +4866,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111273656</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4763,6 +4968,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111315147</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4871,6 +5081,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104622646</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4979,6 +5194,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104622738</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5087,6 +5307,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104622742</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5200,6 +5425,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107173567</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5303,6 +5533,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111268512</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5405,6 +5640,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111273658</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5506,6 +5746,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104681102</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5611,6 +5856,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104681082</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5717,6 +5967,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104680978</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5823,6 +6078,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104680984</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5925,6 +6185,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104680987</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6031,6 +6296,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104681033</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6137,6 +6407,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104681045</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6243,6 +6518,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104681051</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6349,6 +6629,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104681090</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6455,6 +6740,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104681096</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6552,6 +6842,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111273666</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6658,6 +6953,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111315139</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6759,8 +7059,75 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111315141</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>